--- a/research/traditional_assets/database/data/australia/australia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06849999999999999</v>
+        <v>0.0601</v>
       </c>
       <c r="E2">
-        <v>0.0345</v>
+        <v>0.01441</v>
       </c>
       <c r="F2">
-        <v>0.19525</v>
+        <v>0.169</v>
       </c>
       <c r="G2">
-        <v>0.09973579568199409</v>
+        <v>0.07302507355201335</v>
       </c>
       <c r="H2">
-        <v>0.09973579568199409</v>
+        <v>0.07302507355201335</v>
       </c>
       <c r="I2">
-        <v>0.0967654986522911</v>
+        <v>0.07053089184560662</v>
       </c>
       <c r="J2">
-        <v>0.06231130620990397</v>
+        <v>0.05386842005905348</v>
       </c>
       <c r="K2">
-        <v>457.18</v>
+        <v>367.37</v>
       </c>
       <c r="L2">
-        <v>0.0610045101545195</v>
+        <v>0.05377274257527188</v>
       </c>
       <c r="M2">
-        <v>304.895</v>
+        <v>336.16</v>
       </c>
       <c r="N2">
-        <v>0.03251554351651399</v>
+        <v>0.04037618458507992</v>
       </c>
       <c r="O2">
-        <v>0.6669036265803403</v>
+        <v>0.9150447777445082</v>
       </c>
       <c r="P2">
-        <v>299.87</v>
+        <v>333.4</v>
       </c>
       <c r="Q2">
-        <v>0.03197965212383624</v>
+        <v>0.04004468092772979</v>
       </c>
       <c r="R2">
-        <v>0.655912332123015</v>
+        <v>0.9075319160519366</v>
       </c>
       <c r="S2">
-        <v>5.024999999999991</v>
+        <v>2.759999999999991</v>
       </c>
       <c r="T2">
-        <v>0.01648108365174894</v>
+        <v>0.008210376011423106</v>
       </c>
       <c r="U2">
-        <v>758.8000000000001</v>
+        <v>635.9</v>
       </c>
       <c r="V2">
-        <v>0.08092226642067209</v>
+        <v>0.07637796221338745</v>
       </c>
       <c r="W2">
-        <v>0.2124248039531636</v>
+        <v>0.1052597523325847</v>
       </c>
       <c r="X2">
-        <v>0.05538973087091237</v>
+        <v>0.08673550431809957</v>
       </c>
       <c r="Y2">
-        <v>0.1570350730822512</v>
+        <v>0.01852424801448518</v>
       </c>
       <c r="Z2">
-        <v>8.227021983148996</v>
+        <v>5.233255558500413</v>
       </c>
       <c r="AA2">
-        <v>0.2833654076095037</v>
+        <v>0.1493728011205205</v>
       </c>
       <c r="AB2">
-        <v>0.05483425945756283</v>
+        <v>0.08599025368710236</v>
       </c>
       <c r="AC2">
-        <v>0.2288564837690178</v>
+        <v>0.06390488613998921</v>
       </c>
       <c r="AD2">
-        <v>291.98</v>
+        <v>271.103</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>291.98</v>
+        <v>271.103</v>
       </c>
       <c r="AG2">
-        <v>-466.8200000000001</v>
+        <v>-364.797</v>
       </c>
       <c r="AH2">
-        <v>0.03019791330536733</v>
+        <v>0.03153532772589997</v>
       </c>
       <c r="AI2">
-        <v>0.1241105509695738</v>
+        <v>0.1213584475243554</v>
       </c>
       <c r="AJ2">
-        <v>-0.0523923466455969</v>
+        <v>-0.04582357051706319</v>
       </c>
       <c r="AK2">
-        <v>-0.2929011532331941</v>
+        <v>-0.2282830507827582</v>
       </c>
       <c r="AL2">
-        <v>4.904</v>
+        <v>3.571</v>
       </c>
       <c r="AM2">
-        <v>4.904</v>
+        <v>3.571</v>
       </c>
       <c r="AN2">
-        <v>0.3906400513753612</v>
+        <v>0.5434014832631789</v>
       </c>
       <c r="AO2">
-        <v>147.8752039151713</v>
+        <v>134.9369924390927</v>
       </c>
       <c r="AP2">
-        <v>-0.6245584929894038</v>
+        <v>-0.7312026458208056</v>
       </c>
       <c r="AQ2">
-        <v>147.8752039151713</v>
+        <v>134.9369924390927</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.006520000000000001</v>
+        <v>0.00447</v>
       </c>
       <c r="E3">
-        <v>0.0111</v>
+        <v>-0.0261</v>
       </c>
       <c r="F3">
-        <v>0.0282</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="G3">
-        <v>0.0929954668740398</v>
+        <v>0.08040693754979469</v>
       </c>
       <c r="H3">
-        <v>0.0929954668740398</v>
+        <v>0.08040693754979469</v>
       </c>
       <c r="I3">
-        <v>0.09045388160764752</v>
+        <v>0.07852750709893566</v>
       </c>
       <c r="J3">
-        <v>0.06311357105211939</v>
+        <v>0.05524200473471005</v>
       </c>
       <c r="K3">
-        <v>330.8</v>
+        <v>271.4</v>
       </c>
       <c r="L3">
-        <v>0.06274301538228098</v>
+        <v>0.05544319830034115</v>
       </c>
       <c r="M3">
-        <v>254</v>
+        <v>248.84</v>
       </c>
       <c r="N3">
-        <v>0.03785225697807847</v>
+        <v>0.04502913394375882</v>
       </c>
       <c r="O3">
-        <v>0.7678355501813785</v>
+        <v>0.9168754605747973</v>
       </c>
       <c r="P3">
-        <v>249.8</v>
+        <v>246.7</v>
       </c>
       <c r="Q3">
-        <v>0.03722635351623623</v>
+        <v>0.04464188773479064</v>
       </c>
       <c r="R3">
-        <v>0.7551390568319226</v>
+        <v>0.9089904200442153</v>
       </c>
       <c r="S3">
-        <v>4.199999999999989</v>
+        <v>2.139999999999986</v>
       </c>
       <c r="T3">
-        <v>0.0165354330708661</v>
+        <v>0.008599903552483469</v>
       </c>
       <c r="U3">
-        <v>503.6</v>
+        <v>411.1</v>
       </c>
       <c r="V3">
-        <v>0.07504880556756031</v>
+        <v>0.07439108247982339</v>
       </c>
       <c r="W3">
-        <v>0.2665162745729939</v>
+        <v>0.1899097333986425</v>
       </c>
       <c r="X3">
-        <v>0.05527795182164199</v>
+        <v>0.08658565266267959</v>
       </c>
       <c r="Y3">
-        <v>0.2112383227513519</v>
+        <v>0.1033240807359629</v>
       </c>
       <c r="Z3">
-        <v>9.177197563098344</v>
+        <v>5.812277368796012</v>
       </c>
       <c r="AA3">
-        <v>0.5792057104579441</v>
+        <v>0.3210818539264774</v>
       </c>
       <c r="AB3">
-        <v>0.05487597888454241</v>
+        <v>0.08607765696596285</v>
       </c>
       <c r="AC3">
-        <v>0.5243297315734017</v>
+        <v>0.2350041969605145</v>
       </c>
       <c r="AD3">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="AG3">
-        <v>-433.6</v>
+        <v>-358.1</v>
       </c>
       <c r="AH3">
-        <v>0.01032402696045898</v>
+        <v>0.009499569830800116</v>
       </c>
       <c r="AI3">
-        <v>0.04669468347675272</v>
+        <v>0.03803372802296376</v>
       </c>
       <c r="AJ3">
-        <v>-0.06908088645307248</v>
+        <v>-0.06929045490605833</v>
       </c>
       <c r="AK3">
-        <v>-0.4355600200904069</v>
+        <v>-0.3645154723127036</v>
       </c>
       <c r="AL3">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AM3">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AN3">
-        <v>0.1427697328166429</v>
+        <v>0.1346544715447154</v>
       </c>
       <c r="AO3">
-        <v>227.0952380952381</v>
+        <v>232.969696969697</v>
       </c>
       <c r="AP3">
-        <v>-0.8843565164185193</v>
+        <v>-0.9098069105691057</v>
       </c>
       <c r="AQ3">
-        <v>227.0952380952381</v>
+        <v>232.969696969697</v>
       </c>
     </row>
     <row r="4">
@@ -862,124 +862,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06849999999999999</v>
+        <v>0.0601</v>
       </c>
       <c r="E4">
-        <v>0.116</v>
+        <v>0.0256</v>
       </c>
       <c r="F4">
-        <v>0.0895</v>
+        <v>0.112</v>
       </c>
       <c r="G4">
-        <v>0.1007194244604317</v>
+        <v>0.08024264353748738</v>
       </c>
       <c r="H4">
-        <v>0.1007194244604317</v>
+        <v>0.08024264353748738</v>
       </c>
       <c r="I4">
-        <v>0.09641301043672106</v>
+        <v>0.07635821848560634</v>
       </c>
       <c r="J4">
-        <v>0.0670337002287571</v>
+        <v>0.0537612456958147</v>
       </c>
       <c r="K4">
-        <v>120.8</v>
+        <v>93.5</v>
       </c>
       <c r="L4">
-        <v>0.06120174283108724</v>
+        <v>0.04975256744532539</v>
       </c>
       <c r="M4">
-        <v>48.725</v>
+        <v>79.42</v>
       </c>
       <c r="N4">
-        <v>0.02089766683822268</v>
+        <v>0.0312627932609038</v>
       </c>
       <c r="O4">
-        <v>0.4033526490066225</v>
+        <v>0.8494117647058824</v>
       </c>
       <c r="P4">
-        <v>47.9</v>
+        <v>78.8</v>
       </c>
       <c r="Q4">
-        <v>0.02054383256133127</v>
+        <v>0.0310187372067391</v>
       </c>
       <c r="R4">
-        <v>0.396523178807947</v>
+        <v>0.8427807486631016</v>
       </c>
       <c r="S4">
-        <v>0.8250000000000028</v>
+        <v>0.6200000000000045</v>
       </c>
       <c r="T4">
-        <v>0.01693175987685999</v>
+        <v>0.007806597834298722</v>
       </c>
       <c r="U4">
-        <v>160.4</v>
+        <v>142.6</v>
       </c>
       <c r="V4">
-        <v>0.06879396122834106</v>
+        <v>0.05613289245788065</v>
       </c>
       <c r="W4">
-        <v>0.2901056676272815</v>
+        <v>0.1765816808309726</v>
       </c>
       <c r="X4">
-        <v>0.0575888373514148</v>
+        <v>0.08907643783239411</v>
       </c>
       <c r="Y4">
-        <v>0.2325168302758667</v>
+        <v>0.08750524299857851</v>
       </c>
       <c r="Z4">
-        <v>5.786572852535913</v>
+        <v>4.449100378787879</v>
       </c>
       <c r="AA4">
-        <v>0.3878953899487562</v>
+        <v>0.2391891785893575</v>
       </c>
       <c r="AB4">
-        <v>0.05407246669964717</v>
+        <v>0.08471320073657593</v>
       </c>
       <c r="AC4">
-        <v>0.333822923249109</v>
+        <v>0.1544759778527815</v>
       </c>
       <c r="AD4">
-        <v>217.3</v>
+        <v>214.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>217.3</v>
+        <v>214.8</v>
       </c>
       <c r="AG4">
-        <v>56.90000000000001</v>
+        <v>72.20000000000002</v>
       </c>
       <c r="AH4">
-        <v>0.08525246184628664</v>
+        <v>0.07796167247386759</v>
       </c>
       <c r="AI4">
-        <v>0.2909748259239422</v>
+        <v>0.2980435687526016</v>
       </c>
       <c r="AJ4">
-        <v>0.02382248272974671</v>
+        <v>0.02763530582561434</v>
       </c>
       <c r="AK4">
-        <v>0.09703274215552525</v>
+        <v>0.1248918872167445</v>
       </c>
       <c r="AL4">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="AM4">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="AN4">
-        <v>1.093058350100604</v>
+        <v>1.424403183023873</v>
       </c>
       <c r="AO4">
-        <v>70.48148148148148</v>
+        <v>80.16759776536313</v>
       </c>
       <c r="AP4">
-        <v>0.2862173038229376</v>
+        <v>0.4787798408488064</v>
       </c>
       <c r="AQ4">
-        <v>70.48148148148148</v>
+        <v>80.16759776536313</v>
       </c>
     </row>
     <row r="5">
@@ -998,116 +998,125 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.379</v>
+      </c>
+      <c r="E5">
+        <v>0.00322</v>
+      </c>
       <c r="F5">
-        <v>0.301</v>
+        <v>0.226</v>
       </c>
       <c r="G5">
-        <v>0.15</v>
+        <v>0.07304347826086957</v>
       </c>
       <c r="H5">
-        <v>0.15</v>
+        <v>0.07304347826086957</v>
       </c>
       <c r="I5">
-        <v>0.1445378151260504</v>
+        <v>0.06539130434782608</v>
       </c>
       <c r="J5">
-        <v>0.09868258991908449</v>
+        <v>0.04233995627884382</v>
       </c>
       <c r="K5">
-        <v>3.68</v>
+        <v>1.16</v>
       </c>
       <c r="L5">
-        <v>0.0773109243697479</v>
+        <v>0.02017391304347826</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>5.62</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05499021526418787</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>4.844827586206897</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>5.62</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05499021526418787</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>4.844827586206897</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="V5">
-        <v>0.1674982181040627</v>
+        <v>0.2015655577299413</v>
       </c>
       <c r="W5">
-        <v>0.08325791855203619</v>
+        <v>0.01829652996845426</v>
       </c>
       <c r="X5">
-        <v>0.05520360858775999</v>
+        <v>0.086391503852598</v>
       </c>
       <c r="Y5">
-        <v>0.02805430996427621</v>
+        <v>-0.06809497388414375</v>
       </c>
       <c r="Z5">
-        <v>1.812228736769969</v>
+        <v>1.406624590244141</v>
       </c>
       <c r="AA5">
-        <v>0.1788354252702513</v>
+        <v>0.05955642365168354</v>
       </c>
       <c r="AB5">
-        <v>0.05494538098132468</v>
+        <v>0.08622262922448666</v>
       </c>
       <c r="AC5">
-        <v>0.1238900442889267</v>
+        <v>-0.02666620557280312</v>
       </c>
       <c r="AD5">
-        <v>1.09</v>
+        <v>0.383</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.09</v>
+        <v>0.383</v>
       </c>
       <c r="AG5">
-        <v>-22.41</v>
+        <v>-20.217</v>
       </c>
       <c r="AH5">
-        <v>0.00770917320885494</v>
+        <v>0.003733562091184699</v>
       </c>
       <c r="AI5">
-        <v>0.01690184524732517</v>
+        <v>0.00495581175678998</v>
       </c>
       <c r="AJ5">
-        <v>-0.1900924590720163</v>
+        <v>-0.2465999048583243</v>
       </c>
       <c r="AK5">
-        <v>-0.5467187118809467</v>
+        <v>-0.356667783991673</v>
       </c>
       <c r="AL5">
-        <v>0.066</v>
+        <v>0.032</v>
       </c>
       <c r="AM5">
-        <v>0.066</v>
+        <v>0.032</v>
       </c>
       <c r="AN5">
-        <v>0.1526610644257703</v>
+        <v>0.09119047619047618</v>
       </c>
       <c r="AO5">
-        <v>104.2424242424242</v>
+        <v>117.5</v>
       </c>
       <c r="AP5">
-        <v>-3.138655462184874</v>
+        <v>-4.813571428571429</v>
       </c>
       <c r="AQ5">
-        <v>104.2424242424242</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="6">
@@ -1126,50 +1135,32 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1.036</v>
-      </c>
       <c r="E6">
-        <v>0.0345</v>
+        <v>0.569</v>
       </c>
       <c r="F6">
-        <v>0.441</v>
-      </c>
-      <c r="G6">
-        <v>0.2553615960099751</v>
-      </c>
-      <c r="H6">
-        <v>0.2553615960099751</v>
-      </c>
-      <c r="I6">
-        <v>0.2548628428927681</v>
-      </c>
-      <c r="J6">
-        <v>0.127431421446384</v>
+        <v>0.292</v>
       </c>
       <c r="K6">
-        <v>1.9</v>
-      </c>
-      <c r="L6">
-        <v>0.009476309226932668</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="N6">
-        <v>0.01114535182331793</v>
+        <v>0.01453154875717017</v>
       </c>
       <c r="O6">
-        <v>1.142105263157895</v>
+        <v>1.740458015267175</v>
       </c>
       <c r="P6">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>0.01114535182331793</v>
+        <v>0.01453154875717017</v>
       </c>
       <c r="R6">
-        <v>1.142105263157895</v>
+        <v>1.740458015267175</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1178,73 +1169,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>71.3</v>
+        <v>61.6</v>
       </c>
       <c r="V6">
-        <v>0.3662044170518747</v>
+        <v>0.3926067558954748</v>
       </c>
       <c r="W6">
-        <v>0.1583333333333333</v>
+        <v>0.03393782383419689</v>
       </c>
       <c r="X6">
-        <v>0.05550150992018275</v>
+        <v>0.08688535597351953</v>
       </c>
       <c r="Y6">
-        <v>0.1028318234131506</v>
-      </c>
-      <c r="Z6">
-        <v>-6.480074981416244</v>
-      </c>
-      <c r="AA6">
-        <v>-0.8257651659610227</v>
+        <v>-0.05294753213932264</v>
       </c>
       <c r="AB6">
-        <v>0.05479254003058326</v>
-      </c>
-      <c r="AC6">
-        <v>-0.8805577059916059</v>
+        <v>0.08590285040824186</v>
       </c>
       <c r="AD6">
-        <v>3.59</v>
+        <v>2.92</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3.59</v>
+        <v>2.92</v>
       </c>
       <c r="AG6">
-        <v>-67.70999999999999</v>
+        <v>-58.68</v>
       </c>
       <c r="AH6">
-        <v>0.01810479600585002</v>
+        <v>0.01827055437367038</v>
       </c>
       <c r="AI6">
-        <v>0.08509125385162361</v>
+        <v>0.06883545497406883</v>
       </c>
       <c r="AJ6">
-        <v>-0.5331915898889676</v>
+        <v>-0.5974343310934637</v>
       </c>
       <c r="AK6">
-        <v>2.326004809343869</v>
+        <v>3.059436913451512</v>
       </c>
       <c r="AL6">
-        <v>0.038</v>
+        <v>0.099</v>
       </c>
       <c r="AM6">
-        <v>0.038</v>
+        <v>0.099</v>
       </c>
       <c r="AN6">
-        <v>0.0701171875</v>
+        <v>-0.05875251509054325</v>
       </c>
       <c r="AO6">
-        <v>1344.736842105263</v>
+        <v>-503.030303030303</v>
       </c>
       <c r="AP6">
-        <v>-1.3224609375</v>
+        <v>1.180684104627767</v>
       </c>
       <c r="AQ6">
-        <v>1344.736842105263</v>
+        <v>-503.030303030303</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0601</v>
+        <v>0.0659</v>
       </c>
       <c r="E2">
-        <v>0.01441</v>
+        <v>0.0827</v>
       </c>
       <c r="F2">
-        <v>0.169</v>
+        <v>0.0859</v>
       </c>
       <c r="G2">
-        <v>0.07302507355201335</v>
+        <v>0.1050532593657233</v>
       </c>
       <c r="H2">
-        <v>0.07302507355201335</v>
+        <v>0.1050532593657233</v>
       </c>
       <c r="I2">
-        <v>0.07053089184560662</v>
+        <v>0.1029484062487407</v>
       </c>
       <c r="J2">
-        <v>0.05386842005905348</v>
+        <v>0.06835330713658379</v>
       </c>
       <c r="K2">
-        <v>367.37</v>
+        <v>491.01</v>
       </c>
       <c r="L2">
-        <v>0.05377274257527188</v>
+        <v>0.06595430306123819</v>
       </c>
       <c r="M2">
-        <v>336.16</v>
+        <v>341.56</v>
       </c>
       <c r="N2">
-        <v>0.04037618458507992</v>
+        <v>0.03521709095033355</v>
       </c>
       <c r="O2">
-        <v>0.9150447777445082</v>
+        <v>0.6956273802977536</v>
       </c>
       <c r="P2">
-        <v>333.4</v>
+        <v>335.77</v>
       </c>
       <c r="Q2">
-        <v>0.04004468092772979</v>
+        <v>0.03462010372524153</v>
       </c>
       <c r="R2">
-        <v>0.9075319160519366</v>
+        <v>0.6838353597686401</v>
       </c>
       <c r="S2">
-        <v>2.759999999999991</v>
+        <v>5.789999999999992</v>
       </c>
       <c r="T2">
-        <v>0.008210376011423106</v>
+        <v>0.01695163368075885</v>
       </c>
       <c r="U2">
-        <v>635.9</v>
+        <v>600</v>
       </c>
       <c r="V2">
-        <v>0.07637796221338745</v>
+        <v>0.06186396114943239</v>
       </c>
       <c r="W2">
-        <v>0.1052597523325847</v>
+        <v>0.07569620253164558</v>
       </c>
       <c r="X2">
-        <v>0.08673550431809957</v>
+        <v>0.07559854645723942</v>
       </c>
       <c r="Y2">
-        <v>0.01852424801448518</v>
+        <v>9.765607440616331e-05</v>
       </c>
       <c r="Z2">
-        <v>5.233255558500413</v>
+        <v>4.647244625333967</v>
       </c>
       <c r="AA2">
-        <v>0.1493728011205205</v>
+        <v>0.3326467164434295</v>
       </c>
       <c r="AB2">
-        <v>0.08599025368710236</v>
+        <v>0.07414918148609827</v>
       </c>
       <c r="AC2">
-        <v>0.06390488613998921</v>
+        <v>0.2593682807684005</v>
       </c>
       <c r="AD2">
-        <v>271.103</v>
+        <v>303.21</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>271.103</v>
+        <v>303.21</v>
       </c>
       <c r="AG2">
-        <v>-364.797</v>
+        <v>-296.79</v>
       </c>
       <c r="AH2">
-        <v>0.03153532772589997</v>
+        <v>0.03031520979492917</v>
       </c>
       <c r="AI2">
-        <v>0.1213584475243554</v>
+        <v>0.1087784000200903</v>
       </c>
       <c r="AJ2">
-        <v>-0.04582357051706319</v>
+        <v>-0.03156699011158371</v>
       </c>
       <c r="AK2">
-        <v>-0.2282830507827582</v>
+        <v>-0.1356810108758761</v>
       </c>
       <c r="AL2">
-        <v>3.571</v>
+        <v>7.823</v>
       </c>
       <c r="AM2">
-        <v>3.571</v>
+        <v>7.823</v>
       </c>
       <c r="AN2">
-        <v>0.5434014832631789</v>
+        <v>0.3876919536114769</v>
       </c>
       <c r="AO2">
-        <v>134.9369924390927</v>
+        <v>97.97008820145724</v>
       </c>
       <c r="AP2">
-        <v>-0.7312026458208056</v>
+        <v>-0.3794831796852025</v>
       </c>
       <c r="AQ2">
-        <v>134.9369924390927</v>
+        <v>97.97008820145724</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medibank Private Limited (ASX:MPL)</t>
+          <t>Generation Development Group Limited (ASX:GDG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00447</v>
+        <v>0.302</v>
       </c>
       <c r="E3">
-        <v>-0.0261</v>
+        <v>0.632</v>
       </c>
       <c r="F3">
-        <v>0.04969999999999999</v>
+        <v>0.348</v>
       </c>
       <c r="G3">
-        <v>0.08040693754979469</v>
+        <v>0.2028639618138425</v>
       </c>
       <c r="H3">
-        <v>0.08040693754979469</v>
+        <v>0.2028639618138425</v>
       </c>
       <c r="I3">
-        <v>0.07852750709893566</v>
+        <v>0.2016706443914081</v>
       </c>
       <c r="J3">
-        <v>0.05524200473471005</v>
+        <v>0.1008353221957041</v>
       </c>
       <c r="K3">
-        <v>271.4</v>
+        <v>2.99</v>
       </c>
       <c r="L3">
-        <v>0.05544319830034115</v>
+        <v>0.0178400954653938</v>
       </c>
       <c r="M3">
-        <v>248.84</v>
+        <v>2.37</v>
       </c>
       <c r="N3">
-        <v>0.04502913394375882</v>
+        <v>0.01045434494927217</v>
       </c>
       <c r="O3">
-        <v>0.9168754605747973</v>
+        <v>0.7926421404682275</v>
       </c>
       <c r="P3">
-        <v>246.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q3">
-        <v>0.04464188773479064</v>
+        <v>0.01045434494927217</v>
       </c>
       <c r="R3">
-        <v>0.9089904200442153</v>
+        <v>0.7926421404682275</v>
       </c>
       <c r="S3">
-        <v>2.139999999999986</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.008599903552483469</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>411.1</v>
+        <v>62.3</v>
       </c>
       <c r="V3">
-        <v>0.07439108247982339</v>
+        <v>0.2748125275694751</v>
       </c>
       <c r="W3">
-        <v>0.1899097333986425</v>
+        <v>0.07569620253164558</v>
       </c>
       <c r="X3">
-        <v>0.08658565266267959</v>
+        <v>0.07488790630403611</v>
       </c>
       <c r="Y3">
-        <v>0.1033240807359629</v>
-      </c>
-      <c r="Z3">
-        <v>5.812277368796012</v>
-      </c>
-      <c r="AA3">
-        <v>0.3210818539264774</v>
+        <v>0.000808296227609473</v>
       </c>
       <c r="AB3">
-        <v>0.08607765696596285</v>
-      </c>
-      <c r="AC3">
-        <v>0.2350041969605145</v>
+        <v>0.07440936837292234</v>
       </c>
       <c r="AD3">
-        <v>53</v>
+        <v>2.53</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>53</v>
+        <v>2.53</v>
       </c>
       <c r="AG3">
-        <v>-358.1</v>
+        <v>-59.77</v>
       </c>
       <c r="AH3">
-        <v>0.009499569830800116</v>
+        <v>0.01103694978842211</v>
       </c>
       <c r="AI3">
-        <v>0.03803372802296376</v>
+        <v>0.0604829070045422</v>
       </c>
       <c r="AJ3">
-        <v>-0.06929045490605833</v>
+        <v>-0.3580542742466902</v>
       </c>
       <c r="AK3">
-        <v>-0.3645154723127036</v>
+        <v>2.919882755251588</v>
       </c>
       <c r="AL3">
-        <v>1.65</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AM3">
-        <v>1.65</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.1346544715447154</v>
+        <v>0.07441176470588234</v>
       </c>
       <c r="AO3">
-        <v>232.969696969697</v>
+        <v>388.5057471264368</v>
       </c>
       <c r="AP3">
-        <v>-0.9098069105691057</v>
+        <v>-1.757941176470588</v>
       </c>
       <c r="AQ3">
-        <v>232.969696969697</v>
+        <v>388.5057471264368</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nib holdings limited (ASX:NHF)</t>
+          <t>Medibank Private Limited (ASX:MPL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,124 +853,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0601</v>
+        <v>0.0265</v>
       </c>
       <c r="E4">
-        <v>0.0256</v>
+        <v>0.028</v>
       </c>
       <c r="F4">
-        <v>0.112</v>
+        <v>0.0266</v>
       </c>
       <c r="G4">
-        <v>0.08024264353748738</v>
+        <v>0.09919210953631498</v>
       </c>
       <c r="H4">
-        <v>0.08024264353748738</v>
+        <v>0.09919210953631498</v>
       </c>
       <c r="I4">
-        <v>0.07635821848560634</v>
+        <v>0.09744802838642423</v>
       </c>
       <c r="J4">
-        <v>0.0537612456958147</v>
+        <v>0.0684895111680572</v>
       </c>
       <c r="K4">
-        <v>93.5</v>
+        <v>340.2</v>
       </c>
       <c r="L4">
-        <v>0.04975256744532539</v>
+        <v>0.06819958703365876</v>
       </c>
       <c r="M4">
-        <v>79.42</v>
+        <v>252.56</v>
       </c>
       <c r="N4">
-        <v>0.0312627932609038</v>
+        <v>0.03779028010533876</v>
       </c>
       <c r="O4">
-        <v>0.8494117647058824</v>
+        <v>0.7423868312757202</v>
       </c>
       <c r="P4">
-        <v>78.8</v>
+        <v>249.3</v>
       </c>
       <c r="Q4">
-        <v>0.0310187372067391</v>
+        <v>0.03730248982523342</v>
       </c>
       <c r="R4">
-        <v>0.8427807486631016</v>
+        <v>0.7328042328042329</v>
       </c>
       <c r="S4">
-        <v>0.6200000000000045</v>
+        <v>3.259999999999991</v>
       </c>
       <c r="T4">
-        <v>0.007806597834298722</v>
+        <v>0.0129078238834336</v>
       </c>
       <c r="U4">
-        <v>142.6</v>
+        <v>279.9</v>
       </c>
       <c r="V4">
-        <v>0.05613289245788065</v>
+        <v>0.04188113478573138</v>
       </c>
       <c r="W4">
-        <v>0.1765816808309726</v>
+        <v>0.2537859007832898</v>
       </c>
       <c r="X4">
-        <v>0.08907643783239411</v>
+        <v>0.07474619026304004</v>
       </c>
       <c r="Y4">
-        <v>0.08750524299857851</v>
+        <v>0.1790397105202498</v>
       </c>
       <c r="Z4">
-        <v>4.449100378787879</v>
+        <v>5.927866904337493</v>
       </c>
       <c r="AA4">
-        <v>0.2391891785893575</v>
+        <v>0.4059967065473794</v>
       </c>
       <c r="AB4">
-        <v>0.08471320073657593</v>
+        <v>0.07454204122112339</v>
       </c>
       <c r="AC4">
-        <v>0.1544759778527815</v>
+        <v>0.331454665326256</v>
       </c>
       <c r="AD4">
-        <v>214.8</v>
+        <v>36.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>214.8</v>
+        <v>36.8</v>
       </c>
       <c r="AG4">
-        <v>72.20000000000002</v>
+        <v>-243.1</v>
       </c>
       <c r="AH4">
-        <v>0.07796167247386759</v>
+        <v>0.005476190476190476</v>
       </c>
       <c r="AI4">
-        <v>0.2980435687526016</v>
+        <v>0.02584088196053648</v>
       </c>
       <c r="AJ4">
-        <v>0.02763530582561434</v>
+        <v>-0.0377478610580581</v>
       </c>
       <c r="AK4">
-        <v>0.1248918872167445</v>
+        <v>-0.2124628561440307</v>
       </c>
       <c r="AL4">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AM4">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AN4">
-        <v>1.424403183023873</v>
+        <v>0.07437348423605497</v>
       </c>
       <c r="AO4">
-        <v>80.16759776536313</v>
+        <v>405.0833333333334</v>
       </c>
       <c r="AP4">
-        <v>0.4787798408488064</v>
+        <v>-0.4913096200485044</v>
       </c>
       <c r="AQ4">
-        <v>80.16759776536313</v>
+        <v>405.0833333333334</v>
       </c>
     </row>
     <row r="5">
@@ -990,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NobleOak Life Limited (ASX:NOL)</t>
+          <t>nib holdings limited (ASX:NHF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,124 +990,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.379</v>
+        <v>0.0659</v>
       </c>
       <c r="E5">
-        <v>0.00322</v>
+        <v>0.0827</v>
       </c>
       <c r="F5">
-        <v>0.226</v>
+        <v>0.0859</v>
       </c>
       <c r="G5">
-        <v>0.07304347826086957</v>
+        <v>0.1019354215937062</v>
       </c>
       <c r="H5">
-        <v>0.07304347826086957</v>
+        <v>0.1019354215937062</v>
       </c>
       <c r="I5">
-        <v>0.06539130434782608</v>
+        <v>0.09889473430184854</v>
       </c>
       <c r="J5">
-        <v>0.04233995627884382</v>
+        <v>0.06667705069692373</v>
       </c>
       <c r="K5">
-        <v>1.16</v>
+        <v>131.1</v>
       </c>
       <c r="L5">
-        <v>0.02017391304347826</v>
+        <v>0.06327525459722959</v>
       </c>
       <c r="M5">
-        <v>5.62</v>
+        <v>77.83</v>
       </c>
       <c r="N5">
-        <v>0.05499021526418787</v>
+        <v>0.03194467246757511</v>
       </c>
       <c r="O5">
-        <v>4.844827586206897</v>
+        <v>0.5936689549961861</v>
       </c>
       <c r="P5">
-        <v>5.62</v>
+        <v>75.3</v>
       </c>
       <c r="Q5">
-        <v>0.05499021526418787</v>
+        <v>0.03090625513052044</v>
       </c>
       <c r="R5">
-        <v>4.844827586206897</v>
+        <v>0.5743707093821511</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.530000000000001</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.03250674547089813</v>
       </c>
       <c r="U5">
-        <v>20.6</v>
+        <v>161.7</v>
       </c>
       <c r="V5">
-        <v>0.2015655577299413</v>
+        <v>0.06636841241175503</v>
       </c>
       <c r="W5">
-        <v>0.01829652996845426</v>
+        <v>0.2591421229491995</v>
       </c>
       <c r="X5">
-        <v>0.086391503852598</v>
+        <v>0.07660610222735648</v>
       </c>
       <c r="Y5">
-        <v>-0.06809497388414375</v>
+        <v>0.182536020721843</v>
       </c>
       <c r="Z5">
-        <v>1.406624590244141</v>
+        <v>4.988923669636407</v>
       </c>
       <c r="AA5">
-        <v>0.05955642365168354</v>
+        <v>0.3326467164434295</v>
       </c>
       <c r="AB5">
-        <v>0.08622262922448666</v>
+        <v>0.07327843567502902</v>
       </c>
       <c r="AC5">
-        <v>-0.02666620557280312</v>
+        <v>0.2593682807684005</v>
       </c>
       <c r="AD5">
-        <v>0.383</v>
+        <v>194.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.383</v>
+        <v>194.2</v>
       </c>
       <c r="AG5">
-        <v>-20.217</v>
+        <v>32.5</v>
       </c>
       <c r="AH5">
-        <v>0.003733562091184699</v>
+        <v>0.07382346232798601</v>
       </c>
       <c r="AI5">
-        <v>0.00495581175678998</v>
+        <v>0.2287396937573616</v>
       </c>
       <c r="AJ5">
-        <v>-0.2465999048583243</v>
+        <v>0.01316375713880676</v>
       </c>
       <c r="AK5">
-        <v>-0.356667783991673</v>
+        <v>0.04728648334060818</v>
       </c>
       <c r="AL5">
-        <v>0.032</v>
+        <v>1.53</v>
       </c>
       <c r="AM5">
-        <v>0.032</v>
+        <v>1.53</v>
       </c>
       <c r="AN5">
-        <v>0.09119047619047618</v>
+        <v>0.9195075757575758</v>
       </c>
       <c r="AO5">
-        <v>117.5</v>
+        <v>133.921568627451</v>
       </c>
       <c r="AP5">
-        <v>-4.813571428571429</v>
+        <v>0.1538825757575758</v>
       </c>
       <c r="AQ5">
-        <v>117.5</v>
+        <v>133.921568627451</v>
       </c>
     </row>
     <row r="6">
@@ -1127,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Generation Development Group Limited (ASX:GDG)</t>
+          <t>NobleOak Life Limited (ASX:NOL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1135,98 +1126,253 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.334</v>
+      </c>
       <c r="E6">
-        <v>0.569</v>
-      </c>
-      <c r="F6">
-        <v>0.292</v>
+        <v>0.197</v>
+      </c>
+      <c r="G6">
+        <v>0.1420899854862119</v>
+      </c>
+      <c r="H6">
+        <v>0.1420899854862119</v>
+      </c>
+      <c r="I6">
+        <v>0.1381712626995646</v>
+      </c>
+      <c r="J6">
+        <v>0.09736041292207727</v>
       </c>
       <c r="K6">
-        <v>1.31</v>
+        <v>5.32</v>
+      </c>
+      <c r="L6">
+        <v>0.07721335268505079</v>
       </c>
       <c r="M6">
-        <v>2.28</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.01453154875717017</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>1.740458015267175</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.01453154875717017</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>1.740458015267175</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>61.6</v>
+        <v>33.2</v>
       </c>
       <c r="V6">
-        <v>0.3926067558954748</v>
+        <v>0.3380855397148677</v>
       </c>
       <c r="W6">
-        <v>0.03393782383419689</v>
+        <v>0.06918075422626788</v>
       </c>
       <c r="X6">
-        <v>0.08688535597351953</v>
+        <v>0.07559854645723942</v>
       </c>
       <c r="Y6">
-        <v>-0.05294753213932264</v>
+        <v>-0.006417792230971539</v>
+      </c>
+      <c r="Z6">
+        <v>1.217744786143514</v>
+      </c>
+      <c r="AA6">
+        <v>0.1185601352126392</v>
       </c>
       <c r="AB6">
-        <v>0.08590285040824186</v>
+        <v>0.07414918148609827</v>
+      </c>
+      <c r="AC6">
+        <v>0.04441095372654091</v>
       </c>
       <c r="AD6">
-        <v>2.92</v>
+        <v>3.88</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.92</v>
+        <v>3.88</v>
       </c>
       <c r="AG6">
-        <v>-58.68</v>
+        <v>-29.32</v>
       </c>
       <c r="AH6">
-        <v>0.01827055437367038</v>
+        <v>0.03800940438871473</v>
       </c>
       <c r="AI6">
-        <v>0.06883545497406883</v>
+        <v>0.04636711281070746</v>
       </c>
       <c r="AJ6">
-        <v>-0.5974343310934637</v>
+        <v>-0.4256678281068526</v>
       </c>
       <c r="AK6">
-        <v>3.059436913451512</v>
+        <v>-0.5808240887480192</v>
       </c>
       <c r="AL6">
-        <v>0.099</v>
+        <v>0.186</v>
       </c>
       <c r="AM6">
-        <v>0.099</v>
+        <v>0.186</v>
       </c>
       <c r="AN6">
-        <v>-0.05875251509054325</v>
+        <v>0.3963227783452503</v>
       </c>
       <c r="AO6">
-        <v>-503.030303030303</v>
+        <v>51.18279569892473</v>
       </c>
       <c r="AP6">
-        <v>1.180684104627767</v>
+        <v>-2.994892747701737</v>
       </c>
       <c r="AQ6">
-        <v>-503.030303030303</v>
+        <v>51.18279569892473</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ClearView Wealth Limited (ASX:CVW)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.117</v>
+      </c>
+      <c r="E7">
+        <v>-0.08449999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0.2182432432432432</v>
+      </c>
+      <c r="H7">
+        <v>0.2182432432432432</v>
+      </c>
+      <c r="I7">
+        <v>0.2168918918918919</v>
+      </c>
+      <c r="J7">
+        <v>0.1600868725868726</v>
+      </c>
+      <c r="K7">
+        <v>11.4</v>
+      </c>
+      <c r="L7">
+        <v>0.07702702702702703</v>
+      </c>
+      <c r="M7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.03461841070023604</v>
+      </c>
+      <c r="O7">
+        <v>0.7719298245614036</v>
+      </c>
+      <c r="P7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.03461841070023604</v>
+      </c>
+      <c r="R7">
+        <v>0.7719298245614036</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>62.9</v>
+      </c>
+      <c r="V7">
+        <v>0.2474429583005507</v>
+      </c>
+      <c r="W7">
+        <v>0.03438914027149322</v>
+      </c>
+      <c r="X7">
+        <v>0.08109646365017992</v>
+      </c>
+      <c r="Y7">
+        <v>-0.0467073233786867</v>
+      </c>
+      <c r="Z7">
+        <v>0.5128560537805807</v>
+      </c>
+      <c r="AA7">
+        <v>0.08210152173697811</v>
+      </c>
+      <c r="AB7">
+        <v>0.07090438012461167</v>
+      </c>
+      <c r="AC7">
+        <v>0.01119714161236644</v>
+      </c>
+      <c r="AD7">
+        <v>65.8</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>65.8</v>
+      </c>
+      <c r="AG7">
+        <v>2.899999999999999</v>
+      </c>
+      <c r="AH7">
+        <v>0.205625</v>
+      </c>
+      <c r="AI7">
+        <v>0.169238683127572</v>
+      </c>
+      <c r="AJ7">
+        <v>0.01127965772073123</v>
+      </c>
+      <c r="AK7">
+        <v>0.008898435102792264</v>
+      </c>
+      <c r="AL7">
+        <v>4.82</v>
+      </c>
+      <c r="AM7">
+        <v>4.82</v>
+      </c>
+      <c r="AN7">
+        <v>2.037151702786378</v>
+      </c>
+      <c r="AO7">
+        <v>6.659751037344399</v>
+      </c>
+      <c r="AP7">
+        <v>0.0897832817337461</v>
+      </c>
+      <c r="AQ7">
+        <v>6.659751037344399</v>
       </c>
     </row>
   </sheetData>
